--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS07_projection_module_ledger.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS07_projection_module_ledger.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>One row per trusted module per transfer direction (155 rows): the frozen-weight signed eigengene correlation against its feature-type-matched null with Benjamini–Hochberg q, the module's age correlation in each cohort, that correlation expressed as a z statistic against same-weight random projections, and whether the two cohorts agree in sign. The final columns give the same sign agreement computed on the raw projected age correlations. These are the reason the reported statistic is standardized: among the modules significant in both cohorts on raw correlations, the three BrainSEQ-to-GTEx region pairs give sign agreement of 8 of 8 (caudate), 8 of 8 (dorsolateral prefrontal cortex to frontal cortex BA9) and 0 of 13 (hippocampus) – two regions unanimous in one direction and one unanimous in the other, which is a property of each target cohort's own age-correlated structure rather than of the modules (Table S11). Backs Fig. 3e.</t>
+          <t>One row per trusted module per transfer direction (155 rows): the frozen-weight signed eigengene correlation against its feature-type-matched null with Benjamini–Hochberg q, the module's age correlation in each cohort, that correlation expressed as a z statistic against same-weight random projections, and whether the two cohorts agree in sign. The final columns give the same sign agreement computed on the raw projected age correlations. These are the reason the reported statistic is standardized: among the modules significant in both cohorts on raw correlations, the three BrainSEQ-to-Genotype-Tissue Expression (GTEx) region pairs give sign agreement of 8 of 8 (caudate), 8 of 8 (dorsolateral prefrontal cortex to frontal cortex BA9) and 0 of 13 (hippocampus) – two regions unanimous in one direction and one unanimous in the other, which is a property of each target cohort's own age-correlated structure rather than of the modules (Data S28). Backs Fig. 3e.</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 by manuscript/_h/build_supplementary_data.py</t>
+          <t>2026-10-04 by manuscript/_h/build_supplementary_data.py</t>
         </is>
       </c>
     </row>

--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS07_projection_module_ledger.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS07_projection_module_ledger.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>One row per trusted module per transfer direction (155 rows): the frozen-weight signed eigengene correlation against its feature-type-matched null with Benjamini–Hochberg q, the module's age correlation in each cohort, that correlation expressed as a z statistic against same-weight random projections, and whether the two cohorts agree in sign. The final columns give the same sign agreement computed on the raw projected age correlations. These are the reason the reported statistic is standardized: among the modules significant in both cohorts on raw correlations, the three BrainSEQ-to-Genotype-Tissue Expression (GTEx) region pairs give sign agreement of 8 of 8 (caudate), 8 of 8 (dorsolateral prefrontal cortex to frontal cortex BA9) and 0 of 13 (hippocampus) – two regions unanimous in one direction and one unanimous in the other, which is a property of each target cohort's own age-correlated structure rather than of the modules (Data S28). Backs Fig. 3e.</t>
+          <t>One row per trusted module per transfer direction (155 rows): the frozen-weight signed eigengene correlation against its feature-type-matched null with Benjamini–Hochberg q, the module's age correlation in each cohort, that correlation expressed as a z statistic against same-weight random projections, and whether the two cohorts agree in sign. The final columns give the same sign agreement computed on the raw projected age correlations. These are the reason the reported statistic is standardized: among the modules significant in both cohorts on raw correlations, the three BrainSEQ-to-Genotype-Tissue Expression (GTEx) region pairs give sign agreement of 8 of 8 (caudate), 8 of 8 (dorsolateral prefrontal cortex to frontal cortex BA9) and 0 of 13 (hippocampus) – two regions unanimous in one direction and one unanimous in the other, which is a property of each target cohort's own age-correlated structure rather than of the modules (Data S27). Backs Fig. 3e.</t>
         </is>
       </c>
     </row>
